--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>37.755</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>38.11</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>37.83</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>38.11</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>37.77</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>38.13</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>38.13</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>37.775</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>37.87</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>38.15</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>37.87</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4641,7 +4653,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>37.775</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>38.18</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>38.18</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,7 +5628,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5627,7 +5643,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>37.795</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>38.21</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6613,7 +6633,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>37.815</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>38.23</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>37.93</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>38.23</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,7 +7623,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>37.835</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>38.25</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,7 +8613,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>37.845</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>38.26</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,7 +9603,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>37.87</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>38.26</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>37.97</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10542,7 +10578,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10557,22 +10593,22 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>10.16</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>10.46</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11528,7 +11568,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11543,22 +11583,22 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>10.165</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>10.46</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12514,7 +12558,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12529,22 +12573,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>10.155</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>10.46</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>10.48</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13500,7 +13548,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13515,22 +13563,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>10.15</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>10.46</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14486,7 +14538,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14501,22 +14553,22 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>10.19</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>10.46</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15472,7 +15528,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15487,22 +15543,22 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>10.245</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>10.46</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16458,7 +16518,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16473,22 +16533,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>10.305</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>10.47</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17444,7 +17508,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17459,22 +17523,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>10.365</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>10.47</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18430,7 +18498,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18445,22 +18513,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>10.435</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>10.47</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>10.73</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19416,7 +19488,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19431,7 +19503,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19441,12 +19513,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>28.55</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>29.38</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20402,7 +20478,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20417,7 +20493,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20427,12 +20503,12 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>28.645</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>29.38</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21388,7 +21468,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21403,7 +21483,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21413,12 +21493,12 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>28.73</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>29.39</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>29.39</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22374,7 +22458,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22389,7 +22473,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22399,12 +22483,12 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>29.37</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>29.18</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23360,7 +23448,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23375,7 +23463,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23385,12 +23473,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>28.905</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>29.38</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>29.28</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24346,7 +24438,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24361,22 +24453,22 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>28.995</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>29.38</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>29.39</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25332,7 +25428,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25347,22 +25443,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>29.07</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>29.49</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>29.4</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>29.49</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26318,7 +26418,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26333,22 +26433,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>29.085</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>29.37</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>29.56</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,22 +27423,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>29.105</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>29.33</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>29.33</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28290,7 +28398,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28305,7 +28413,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28315,12 +28423,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>10.8</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>11.12</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>10.92</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>11.12</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29276,7 +29388,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29291,7 +29403,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29301,12 +29413,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>10.815</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>11.13</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>10.94</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>11.13</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30262,7 +30378,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30277,7 +30393,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -30287,12 +30403,12 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>10.81</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>11.14</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31248,7 +31368,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31263,7 +31383,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -31273,12 +31393,12 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>10.81</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>11.14</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>10.99</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32234,7 +32358,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32249,7 +32373,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -32259,12 +32383,12 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>10.83</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>11.14</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33220,7 +33348,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33235,7 +33363,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -33245,12 +33373,12 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>10.87</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>11.15</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34206,7 +34338,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34221,22 +34353,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>10.91</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>11.16</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>11.16</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35192,7 +35328,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35207,22 +35343,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>10.935</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>11.16</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>11.16</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,7 +36318,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36193,22 +36333,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>10.97</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>11.17</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>11.18</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37164,7 +37308,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37179,22 +37323,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>13.085</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>13.31</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38150,7 +38298,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38165,22 +38313,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>13.34</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -39136,7 +39288,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -39151,22 +39303,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>13.135</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>13.37</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>13.28</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -40122,7 +40278,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -40137,22 +40293,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>13.145</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>13.38</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -41108,7 +41268,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -41123,22 +41283,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>13.18</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>13.42</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -42094,7 +42258,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -42109,22 +42273,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>13.45</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -43080,7 +43248,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -43095,22 +43263,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>13.235</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>13.48</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>13.48</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -44066,7 +44238,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -44081,22 +44253,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>13.24</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>13.52</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>13.52</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45052,7 +45228,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -45067,22 +45243,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>13.24</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>13.56</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>13.56</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -46038,7 +46218,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -46053,7 +46233,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -46063,12 +46243,12 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46267,11 +46447,15 @@
           <t>24.62</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>24.03</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>24.68</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>24.03</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -47024,7 +47208,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -47039,7 +47223,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -47049,12 +47233,12 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47253,11 +47437,15 @@
           <t>24.64</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>23.98</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>23.98</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -48010,7 +48198,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -48025,7 +48213,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -48035,12 +48223,12 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48239,11 +48427,15 @@
           <t>24.67</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>23.92</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>24.73</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>23.92</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48996,7 +49188,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -49011,7 +49203,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -49021,12 +49213,12 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49225,11 +49417,15 @@
           <t>24.69</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>23.86</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>24.76</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>23.86</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49982,7 +50178,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -49997,7 +50193,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -50007,12 +50203,12 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50211,11 +50407,15 @@
           <t>24.745</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>23.81</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>23.81</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50968,7 +51168,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50983,7 +51183,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -50993,12 +51193,12 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -51197,11 +51397,15 @@
           <t>24.81</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>23.76</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>24.83</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>23.76</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51954,7 +52158,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -51969,22 +52173,22 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -52183,11 +52387,15 @@
           <t>24.78</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>23.71</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>24.86</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52940,7 +53148,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -52955,22 +53163,22 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -53169,11 +53377,15 @@
           <t>24.725</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>23.66</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>24.88</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53926,7 +54138,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53941,22 +54153,22 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -54155,11 +54367,15 @@
           <t>24.715</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>23.6</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54912,7 +55128,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54927,7 +55143,7 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -54937,12 +55153,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -55141,11 +55357,15 @@
           <t>47.195</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>47.64</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>47.35</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>47.64</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55898,7 +56118,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55913,7 +56133,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -55923,12 +56143,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -56127,11 +56347,15 @@
           <t>47.15499999999999</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>47.66</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>47.36</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>47.66</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56884,7 +57108,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56899,7 +57123,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -56909,12 +57133,12 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -57113,11 +57337,15 @@
           <t>47.11</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>47.69</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>47.69</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57870,7 +58098,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57885,7 +58113,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -57895,12 +58123,12 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -58099,11 +58327,15 @@
           <t>47.08</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>47.71</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>47.71</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58856,7 +59088,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58871,7 +59103,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -58881,12 +59113,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -59085,11 +59317,15 @@
           <t>47.12</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>47.74</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>47.43</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>47.74</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59842,7 +60078,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59857,7 +60093,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -59867,12 +60103,12 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -60071,11 +60307,15 @@
           <t>47.16</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>47.77</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>47.77</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60828,7 +61068,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60843,22 +61083,22 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -61057,11 +61297,15 @@
           <t>47.19500000000001</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>47.79</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>47.55</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>47.79</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61814,7 +62058,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61829,22 +62073,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -62043,11 +62287,15 @@
           <t>47.265</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>47.81</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>47.62</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>47.81</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62800,7 +63048,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62815,22 +63063,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -63029,11 +63277,15 @@
           <t>47.315</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>47.84</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>47.71</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>47.84</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
